--- a/outputs/bulk-excel-templates-20260818/고등학교_학생증_단체신청_양식_v1.2.xlsx
+++ b/outputs/bulk-excel-templates-20260818/고등학교_학생증_단체신청_양식_v1.2.xlsx
@@ -403,7 +403,7 @@
     <x:t>국가코드를 포함한 E.164 형식으로 입력합니다. 예: +821012345678, +12025550123</x:t>
   </x:si>
   <x:si>
-    <x:t>ZIP 루트에 .xlsx 파일 정확히 1개와 신청자 사진을 둡니다. __MACOSX와 .DS_Store는 무시되지만 하위 폴더 파일은 사진으로 인정하지 않습니다. 신청자 사진은 JPG(.jpg) 또는 PNG(.png) 중 하나로 준비합니다. 사진은 한 형식으로 통일해야 합니다. 모두 PNG이면 PNG 파일만, 모두 JPG이면 JPG 파일만 ZIP 루트에 넣어 주세요. 두 형식을 섞으면 안 됩니다.</x:t>
+    <x:t>ZIP 루트에 .xlsx 파일 정확히 1개와 신청자 사진을 둡니다. 엑셀 파일은 반드시 .xlsx 확장자로 저장해 제출해야 합니다. 이 양식은 .xlsx 형식으로 만들었으므로 .xls 등 다른 확장자는 지원하지 않습니다. 신청자 사진은 JPG(.jpg) 또는 PNG(.png) 중 하나로 준비합니다. 사진은 한 형식으로 통일해야 합니다. 모두 PNG이면 PNG 파일만, 모두 JPG이면 JPG 파일만 ZIP 루트에 넣어 주세요. 두 형식을 섞으면 안 됩니다.</x:t>
   </x:si>
   <x:si>
     <x:t>007</x:t>
@@ -1576,7 +1576,7 @@
     <x:t>발급 카드 조회와 국제 안내 발송을 위해 모든 신청자의 이메일과 전화번호를 받습니다. 동일 연락처를 여러 신청자가 공유할 수 있습니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>신청자명단에 자동 표시된 사진 번호와 같은 파일명으로 사진을 준비합니다. 예: 사진 번호가 001이면 001.jpg</x:t>
+    <x:t>신청자명단에 자동 표시된 사진 번호와 같은 파일명으로 사진을 준비합니다. 예: 사진 번호가 001이면 001.jpg. 이 파일명 규칙은 반드시 지켜야 하며, 어기면 신청 전체가 접수되지 않습니다.</x:t>
   </x:si>
   <x:si>
     <x:t>필수값·형식·사진 번호·사진·양식 버전·헤더 중 하나라도 잘못되면 일부 인원만 접수하지 않고 신청 전체가 실패합니다.</x:t>

--- a/outputs/bulk-excel-templates-20260818/고등학교_학생증_단체신청_양식_v1.2.xlsx
+++ b/outputs/bulk-excel-templates-20260818/고등학교_학생증_단체신청_양식_v1.2.xlsx
@@ -1573,7 +1573,7 @@
     <x:t>사진 누락, Excel에 없는 여분 사진, 001.jpg와 001.png 같은 동일 ID 중복은 모두 신청 전체 실패 사유입니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>발급 카드 조회와 국제 안내 발송을 위해 모든 신청자의 이메일과 전화번호를 받습니다. 동일 연락처를 여러 신청자가 공유할 수 있습니다.</x:t>
+    <x:t>발급 카드 조회와 국제 안내 발송을 위해 모든 신청자의 이메일과 전화번호를 받습니다. 구성원마다 전화번호와 이메일이 같은 조합이 있으면 안 됩니다. 전화번호와 이메일이 모두 같은 구성원이 두 명 이상 있으면 신청 전체가 접수되지 않습니다.</x:t>
   </x:si>
   <x:si>
     <x:t>신청자명단에 자동 표시된 사진 번호와 같은 파일명으로 사진을 준비합니다. 예: 사진 번호가 001이면 001.jpg. 이 파일명 규칙은 반드시 지켜야 하며, 어기면 신청 전체가 접수되지 않습니다.</x:t>

--- a/outputs/bulk-excel-templates-20260818/고등학교_학생증_단체신청_양식_v1.2.xlsx
+++ b/outputs/bulk-excel-templates-20260818/고등학교_학생증_단체신청_양식_v1.2.xlsx
@@ -1573,7 +1573,7 @@
     <x:t>사진 누락, Excel에 없는 여분 사진, 001.jpg와 001.png 같은 동일 ID 중복은 모두 신청 전체 실패 사유입니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>발급 카드 조회와 국제 안내 발송을 위해 모든 신청자의 이메일과 전화번호를 받습니다. 구성원마다 전화번호와 이메일이 같은 조합이 있으면 안 됩니다. 전화번호와 이메일이 모두 같은 구성원이 두 명 이상 있으면 신청 전체가 접수되지 않습니다.</x:t>
+    <x:t>발급 카드 조회와 국제 안내 발송을 위해 모든 신청자의 이메일과 전화번호를 받습니다. 구성원마다 전화번호와 이메일이 같은 조합이 있으면 안 됩니다. 전화번호와 이메일이 둘 다 같은 구성원이 두 명 이상이면 오류가 나고, 신청이 접수되지 않습니다.</x:t>
   </x:si>
   <x:si>
     <x:t>신청자명단에 자동 표시된 사진 번호와 같은 파일명으로 사진을 준비합니다. 예: 사진 번호가 001이면 001.jpg. 이 파일명 규칙은 반드시 지켜야 하며, 어기면 신청 전체가 접수되지 않습니다.</x:t>
